--- a/output/pdf_financials_xlsx/MEDA.xlsx
+++ b/output/pdf_financials_xlsx/MEDA.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.001562</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.101855</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.153518</v>
       </c>
     </row>
     <row r="93">
@@ -3098,7 +3098,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3497,7 +3501,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>2.001562</v>
       </c>

--- a/output/pdf_financials_xlsx/MEDA.xlsx
+++ b/output/pdf_financials_xlsx/MEDA.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.157835</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.619403</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017494</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.157835</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.619403</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.017494</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.361744</v>
+        <v>0.203909</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.644061</v>
+        <v>0.024658</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.035559</v>
+        <v>0.018065</v>
       </c>
     </row>
     <row r="49">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/MEDA.xlsx
+++ b/output/pdf_financials_xlsx/MEDA.xlsx
@@ -752,10 +752,10 @@
         <v>-6.046235</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.180413</v>
+        <v>-4.163464</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.002854</v>
+        <v>-0.910556</v>
       </c>
     </row>
     <row r="21">
@@ -768,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.180413</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>0.002854</v>
       </c>
     </row>
     <row r="22">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.58638</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.639202</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.082096</v>
       </c>
     </row>
     <row r="68">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.059503</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.059503</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-5.915405</v>
+        <v>-5.974908</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.160154</v>
@@ -4693,7 +4693,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>-0.059503</v>
       </c>
@@ -5734,7 +5738,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -5765,7 +5773,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
